--- a/papers/zodiac/zodiac-donnees.xlsx
+++ b/papers/zodiac/zodiac-donnees.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Étoiles principales" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Étoiles secondaires" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secteurs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phases comparées" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moindres carrés" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Villes de référence" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +91,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sens inverse (ciel vu d'en bas) : longitude terrestre = φ − longitude écliptique J2000.</t>
+          <t>Sens inverse (ciel vu d'en bas) : longitude terrestre = φ − longitude écliptique J2000. φ est l'équilibre par moindres carrés de 26 couples ciel – terre.</t>
         </is>
       </c>
     </row>
@@ -489,7 +493,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Entrée modifiable. 206,178 = Spica (203,841°) posée sur le méridien de Paris (2,337° E). Toutes les colonnes « Méridien » et « Secteurs » se recalculent.</t>
+          <t>Entrée modifiable. 206,178 : équilibre des 26 couples étoile – lieu, Sphinx compris (optimum 206,187°, onglet « Moindres carrés »). Avec cet angle, Spica (203,841°) tombe sur le méridien de Paris (2,337° E). Toutes les colonnes « Méridien » et « Secteurs » se recalculent.</t>
         </is>
       </c>
     </row>
@@ -527,7 +531,6 @@
           <t>Onglets</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -568,12 +571,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Phases comparées</t>
+          <t>Moindres carrés</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Calages candidats et score de moindre carré robuste (écarts plafonnés à 1°)</t>
+          <t>Les 26 couples étoile – lieu (Sphinx compris), leurs écarts et l'angle optimal, recalculés à partir de la phase</t>
         </is>
       </c>
     </row>
@@ -585,7 +588,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>45 villes historiques figées utilisées pour le calcul de phase</t>
+          <t>45 villes historiques de référence</t>
         </is>
       </c>
     </row>
@@ -595,7 +598,6 @@
           <t>Sources</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1190,7 +1192,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Point d'ancrage (calage)</t>
+          <t>Signature : l'épi sur Paris à 0,01°</t>
         </is>
       </c>
     </row>
@@ -3031,193 +3033,965 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Calages comparés</t>
+          <t>L'équilibre par moindres carrés</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25 étoiles (paires &lt; 0,3° fusionnées) contre 45 villes historiques ; coût = Σ min(écart, 1°)² ; rang sur 36 000 phases (pas 0,01°).</t>
+          <t>Étoiles et lieux restent rigides ; seule la rotation φ varie. Écart = méridien de l'étoile (φ − λ) − longitude du lieu. L'angle optimal rend minimale la somme des carrés des écarts : φ* = φ − moyenne des écarts.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Calage</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>φ (°)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Spica tombe à (°, Est +)</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Étoiles à &lt; 1° d'une ville</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Coût robuste</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Rang / 36 000</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Couple (étoile ou point du ciel)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>λ écliptique (°)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Lieu</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Longitude du lieu (°, Est +)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Méridien de l'étoile (°)</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Écart (°)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Inclus (&lt; 1° à 206,178)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spica sur Paris (calage retenu)</t>
+          <t>Hamal</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>206.178</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6988</v>
+        <v>37.66</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Port-Vila</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>168.318</v>
+      </c>
+      <c r="E5" s="4">
+        <f>MOD(Phase-B5+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F5" s="4">
+        <f>MOD(E5-D5+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Réglage Meta AI V3</t>
+          <t>Alcyone</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>206.41</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8396</v>
+        <v>59.99</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>144.988</v>
+      </c>
+      <c r="E6" s="4">
+        <f>MOD(Phase-B6+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F6" s="4">
+        <f>MOD(E6-D6+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Phase A : Lion de Londres à Jérusalem</t>
+          <t>Aldebaran</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>173.49</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-30.35</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="F7" t="n">
-        <v>12</v>
+        <v>69.79000000000001</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ise</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>136.728</v>
+      </c>
+      <c r="E7" s="4">
+        <f>MOD(Phase-B7+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F7" s="4">
+        <f>MOD(E7-D7+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Phase « Spica sur Delhi »</t>
+          <t>Elnath</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>280.9</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>77.06</v>
-      </c>
-      <c r="D8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>17.46</v>
-      </c>
-      <c r="F8" t="n">
-        <v>98</v>
+        <v>82.56999999999999</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Shenyang</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>123.438</v>
+      </c>
+      <c r="E8" s="4">
+        <f>MOD(Phase-B8+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F8" s="4">
+        <f>MOD(E8-D8+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meilleur score robuste (Spica sur Pagan)</t>
+          <t>Castor</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>298.98</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>95.14</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
+        <v>110.24</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yangon</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>96.13800000000001</v>
+      </c>
+      <c r="E9" s="4">
+        <f>MOD(Phase-B9+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F9" s="4">
+        <f>MOD(E9-D9+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Moindre carré brut (non robuste)</t>
+          <t>Pollux</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>196.43</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-7.41</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="F10" t="n">
-        <v>20858</v>
+        <v>113.22</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Krasnoïarsk</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>92.928</v>
+      </c>
+      <c r="E10" s="4">
+        <f>MOD(Phase-B10+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>MOD(E10-D10+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Asellus Australis</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>128.72</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bhopal</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>77.408</v>
+      </c>
+      <c r="E11" s="4">
+        <f>MOD(Phase-B11+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F11" s="4">
+        <f>MOD(E11-D11+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Acubens</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>133.64</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>72.58799999999999</v>
+      </c>
+      <c r="E12" s="4">
+        <f>MOD(Phase-B12+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F12" s="4">
+        <f>MOD(E12-D12+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regulus</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>149.83</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ormuz (Bandar Abbas)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>56.268</v>
+      </c>
+      <c r="E13" s="4">
+        <f>MOD(Phase-B13+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F13" s="4">
+        <f>MOD(E13-D13+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Algieba</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>149.62</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ormuz (Bandar Abbas)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>56.268</v>
+      </c>
+      <c r="E14" s="4">
+        <f>MOD(Phase-B14+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F14" s="4">
+        <f>MOD(E14-D14+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Denebola</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>171.62</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jérusalem</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>35.218</v>
+      </c>
+      <c r="E15" s="4">
+        <f>MOD(Phase-B15+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F15" s="4">
+        <f>MOD(E15-D15+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vindemiatrix</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>189.94</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vienne</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>16.368</v>
+      </c>
+      <c r="E16" s="4">
+        <f>MOD(Phase-B16+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>MOD(E16-D16+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spica</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>203.84</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2.348</v>
+      </c>
+      <c r="E17" s="4">
+        <f>MOD(Phase-B17+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F17" s="4">
+        <f>MOD(E17-D17+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Zubeneschamali</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>229.37</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Praia</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-23.512</v>
+      </c>
+      <c r="E18" s="4">
+        <f>MOD(Phase-B18+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F18" s="4">
+        <f>MOD(E18-D18+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Antares</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>249.76</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-43.182</v>
+      </c>
+      <c r="E19" s="4">
+        <f>MOD(Phase-B19+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F19" s="4">
+        <f>MOD(E19-D19+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shaula</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>264.59</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-58.382</v>
+      </c>
+      <c r="E20" s="4">
+        <f>MOD(Phase-B20+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f>MOD(E20-D20+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sabik</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>257.97</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nuuk</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-51.742</v>
+      </c>
+      <c r="E21" s="4">
+        <f>MOD(Phase-B21+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F21" s="4">
+        <f>MOD(E21-D21+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rasalhague</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>262.45</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-56.192</v>
+      </c>
+      <c r="E22" s="4">
+        <f>MOD(Phase-B22+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F22" s="4">
+        <f>MOD(E22-D22+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kaus Australis</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>275.08</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>-68.152</v>
+      </c>
+      <c r="E23" s="4">
+        <f>MOD(Phase-B23+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f>MOD(E23-D23+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Nunki</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>282.39</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-76.52200000000001</v>
+      </c>
+      <c r="E24" s="4">
+        <f>MOD(Phase-B24+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F24" s="4">
+        <f>MOD(E24-D24+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dabih</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>304.05</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-97.742</v>
+      </c>
+      <c r="E25" s="4">
+        <f>MOD(Phase-B25+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F25" s="4">
+        <f>MOD(E25-D25+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Deneb Algedi</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>323.54</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>-117.162</v>
+      </c>
+      <c r="E26" s="4">
+        <f>MOD(Phase-B26+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F26" s="4">
+        <f>MOD(E26-D26+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sadalsuud</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>323.4</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-117.172</v>
+      </c>
+      <c r="E27" s="4">
+        <f>MOD(Phase-B27+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F27" s="4">
+        <f>MOD(E27-D27+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Alpherg (η Psc)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Suva (Fidji)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>178.458</v>
+      </c>
+      <c r="E28" s="4">
+        <f>MOD(Phase-B28+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F28" s="4">
+        <f>MOD(E28-D28+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Alrescha</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Suva (Fidji)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>178.398</v>
+      </c>
+      <c r="E29" s="4">
+        <f>MOD(Phase-B29+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F29" s="4">
+        <f>MOD(E29-D29+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Porte Vierge – Lion (limite UAI)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>174.15</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sphinx de Gizeh</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>31.138</v>
+      </c>
+      <c r="E30" s="4">
+        <f>MOD(Phase-B30+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F30" s="4">
+        <f>MOD(E30-D30+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Ajustement</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>φ optimal (°)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Écart quadratique moyen (°)</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Δ avec la phase (°)</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Spica tombe à (°, Est +)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Équilibre des 26 couples, Sphinx compris</t>
+        </is>
+      </c>
+      <c r="B33" s="9">
+        <f>Phase-AVERAGE(F5:F30)</f>
+        <v/>
+      </c>
+      <c r="C33" s="4">
+        <f>SQRT(SUMPRODUCT((F5:F30-AVERAGE(F5:F30))^2)/COUNT(F5:F30))</f>
+        <v/>
+      </c>
+      <c r="D33" s="9">
+        <f>ABS(B33-Phase)</f>
+        <v/>
+      </c>
+      <c r="E33" s="4">
+        <f>MOD(B33-203.841+180,360)-180</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Les 25 couples étoile – lieu, sans le Sphinx</t>
+        </is>
+      </c>
+      <c r="B34" s="9">
+        <f>Phase-AVERAGE(F5:F29)</f>
+        <v/>
+      </c>
+      <c r="C34" s="4">
+        <f>SQRT(SUMPRODUCT((F5:F29-AVERAGE(F5:F29))^2)/COUNT(F5:F29))</f>
+        <v/>
+      </c>
+      <c r="D34" s="9">
+        <f>ABS(B34-Phase)</f>
+        <v/>
+      </c>
+      <c r="E34" s="4">
+        <f>MOD(B34-203.841+180,360)-180</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Couples à moins d'un degré, Sphinx compris</t>
+        </is>
+      </c>
+      <c r="B35" s="9">
+        <f>Phase-AVERAGEIF(G5:G30,"oui",F5:F30)</f>
+        <v/>
+      </c>
+      <c r="D35" s="9">
+        <f>ABS(B35-Phase)</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f>MOD(B35-203.841+180,360)-180</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3231,7 +4005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>

--- a/papers/zodiac/zodiac-donnees.xlsx
+++ b/papers/zodiac/zodiac-donnees.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Étoiles secondaires" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secteurs" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moindres carrés" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Villes de référence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Villes de référence" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="Phase">Paramètres!$B$4</definedName>
@@ -460,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -583,53 +584,65 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Portes</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Les 13 méridiens de passage d'un signe à l'autre, leurs lieux gardiens et l'angle optimal qu'ils donnent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Villes de référence</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>45 villes historiques de référence</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Positions</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Catalogue PyEphem 4.2.1 ; coordonnées J2000 Wikipédia pour les étoiles absentes du catalogue</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bornes</t>
+          <t>Positions</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Limites UAI (Delporte 1930), valeurs J2000 arrondies</t>
+          <t>Catalogue PyEphem 4.2.1 ; coordonnées J2000 Wikipédia pour les étoiles absentes du catalogue</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Bornes</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Limites UAI (Delporte 1930), valeurs J2000 arrondies</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Villes</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>GeoNames (villes ≥ 500 000 hab.) et longitudes usuelles des sites historiques</t>
         </is>
@@ -4005,6 +4018,646 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Les portes de la roue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Les 13 méridiens où un signe passe au suivant, et le lieu remarquable le plus proche. « Gardée » : un monument ou un lieu sacré à moins d'un degré. L'angle optimal se recalcule à partir de la phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Porte</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>λ de la frontière (°)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Lieu</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Longitude du lieu (°, Est +)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Méridien de la porte (°)</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Écart (°)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Gardée</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Nature du lieu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bélier | Taureau</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>153.03</v>
+      </c>
+      <c r="E5" s="4">
+        <f>MOD(Phase-B5+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F5" s="4">
+        <f>MOD(E5-D5+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ville moderne</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Taureau | Gémeaux</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Grande Muraille, Badaling</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>116.016</v>
+      </c>
+      <c r="E6" s="4">
+        <f>MOD(Phase-B6+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F6" s="4">
+        <f>MOD(E6-D6+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Frontière bâtie de la Chine ; Cité interdite à 0,65°</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gémeaux | Cancer</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>118.26</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kangchenjunga</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>88.14700000000001</v>
+      </c>
+      <c r="E7" s="4">
+        <f>MOD(Phase-B7+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F7" s="4">
+        <f>MOD(E7-D7+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Troisième sommet du monde, montagne sacrée du Sikkim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cancer | Lion</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>138.18</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mohenjo-daro</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>68.13800000000001</v>
+      </c>
+      <c r="E8" s="4">
+        <f>MOD(Phase-B8+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F8" s="4">
+        <f>MOD(E8-D8+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cité de l'Indus, le Grand Bain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lion | Vierge</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>174.15</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sphinx de Gizeh</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>31.138</v>
+      </c>
+      <c r="E9" s="4">
+        <f>MOD(Phase-B9+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F9" s="4">
+        <f>MOD(E9-D9+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Le gardien à corps de lion ; Léontopolis à 0,69°</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vierge | Balance</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>218.13</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ouadane</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-11.62</v>
+      </c>
+      <c r="E10" s="4">
+        <f>MOD(Phase-B10+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>MOD(E10-D10+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ksar caravanier, UNESCO ; Chinguetti à 0,41°</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Balance | Scorpion</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>241.05</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Olinda</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-34.855</v>
+      </c>
+      <c r="E11" s="4">
+        <f>MOD(Phase-B11+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F11" s="4">
+        <f>MOD(E11-D11+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ville historique, UNESCO ; Ponta do Seixas, point le plus oriental des Amériques, à 0,08°</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Scorpion | Ophiuchus</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>247.68</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cabo Frio</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-42.02</v>
+      </c>
+      <c r="E12" s="4">
+        <f>MOD(Phase-B12+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F12" s="4">
+        <f>MOD(E12-D12+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ophiuchus | Sagittaire</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>266.25</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rencontre des eaux, Manaus</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-59.9</v>
+      </c>
+      <c r="E13" s="4">
+        <f>MOD(Phase-B13+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F13" s="4">
+        <f>MOD(E13-D13+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Rio Negro et Solimões côte à côte sans se mêler</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sagittaire | Capricorne</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>299.71</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>La Venta</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-94.04000000000001</v>
+      </c>
+      <c r="E14" s="4">
+        <f>MOD(Phase-B14+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F14" s="4">
+        <f>MOD(E14-D14+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Grande cité olmèque, pyramide et têtes colossales</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Capricorne | Verseau</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>327.88</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mont Hood (Wy'east)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-121.696</v>
+      </c>
+      <c r="E15" s="4">
+        <f>MOD(Phase-B15+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F15" s="4">
+        <f>MOD(E15-D15+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Montagne de la légende du Pont des Dieux</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Verseau | Poissons</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Valdez</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-146.35</v>
+      </c>
+      <c r="E16" s="4">
+        <f>MOD(Phase-B16+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>MOD(E16-D16+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Port d'Alaska</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Poissons | Bélier</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Whakaari</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>177.18</v>
+      </c>
+      <c r="E17" s="4">
+        <f>MOD(Phase-B17+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F17" s="4">
+        <f>MOD(E17-D17+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Volcan actif de Nouvelle-Zélande</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Ajustement</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>φ optimal (°)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Écart quadratique moyen (°)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Δ avec la phase (°)</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Spica tombe à (°, Est +)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Les 10 portes gardées</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>Phase-AVERAGEIF(G5:G17,"oui",F5:F17)</f>
+        <v/>
+      </c>
+      <c r="C20" s="4">
+        <f>SQRT(SUMPRODUCT((G5:G17="oui")*(F5:F17-AVERAGEIF(G5:G17,"oui",F5:F17))^2)/COUNTIF(G5:G17,"oui"))</f>
+        <v/>
+      </c>
+      <c r="D20" s="9">
+        <f>ABS(B20-Phase)</f>
+        <v/>
+      </c>
+      <c r="E20" s="4">
+        <f>MOD(B20-203.841+180,360)-180</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Les 13 portes</t>
+        </is>
+      </c>
+      <c r="B21" s="9">
+        <f>Phase-AVERAGE(F5:F17)</f>
+        <v/>
+      </c>
+      <c r="C21" s="4">
+        <f>SQRT(SUMPRODUCT((F5:F17-AVERAGE(F5:F17))^2)/COUNT(F5:F17))</f>
+        <v/>
+      </c>
+      <c r="D21" s="9">
+        <f>ABS(B21-Phase)</f>
+        <v/>
+      </c>
+      <c r="E21" s="4">
+        <f>MOD(B21-203.841+180,360)-180</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>25 couples étoile – lieu + 10 portes gardées</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>Phase-(SUM('Moindres carrés'!F5:F29)+SUMIF(G5:G17,"oui",F5:F17))/(25+COUNTIF(G5:G17,"oui"))</f>
+        <v/>
+      </c>
+      <c r="D22" s="9">
+        <f>ABS(B22-Phase)</f>
+        <v/>
+      </c>
+      <c r="E22" s="4">
+        <f>MOD(B22-203.841+180,360)-180</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/papers/zodiac/zodiac-donnees.xlsx
+++ b/papers/zodiac/zodiac-donnees.xlsx
@@ -24,10 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +51,7 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -81,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,6 +98,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sens inverse (ciel vu d'en bas) : longitude terrestre = φ − longitude écliptique J2000. φ est l'équilibre par moindres carrés de 26 couples ciel – terre.</t>
+          <t>Sens inverse (ciel vu d'en bas) : longitude terrestre = φ − longitude écliptique J2000. φ est l'optimum des moindres carrés entre 27 étoiles et 45 lieux de référence.</t>
         </is>
       </c>
     </row>
@@ -490,11 +494,11 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>206.178</v>
+        <v>198.716</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Entrée modifiable. 206,178 : équilibre des 26 couples étoile – lieu, Sphinx compris (optimum 206,187°, onglet « Moindres carrés »). Avec cet angle, Spica (203,841°) tombe sur le méridien de Paris (2,337° E). Toutes les colonnes « Méridien » et « Secteurs » se recalculent.</t>
+          <t>Entrée modifiable. 198,716 : optimum des moindres carrés (27 étoiles contre les 45 lieux de référence, 7 200 positions balayées). Spica tombe alors sur Ouessant.</t>
         </is>
       </c>
     </row>
@@ -522,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Entrée à modifier. Les colonnes de villes et d'écarts sont valables pour φ = 206,178 seulement.</t>
+          <t>Entrée à modifier. Les colonnes de villes et d'écarts sont valables pour φ = 198,716 seulement.</t>
         </is>
       </c>
     </row>
@@ -577,7 +581,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Les 26 couples étoile – lieu (Sphinx compris), leurs écarts et l'angle optimal, recalculés à partir de la phase</t>
+          <t>Les 27 étoiles face au lieu de référence le plus proche à φ = 198,716, leurs écarts, la somme des carrés, et les vallées du balayage</t>
         </is>
       </c>
     </row>
@@ -589,7 +593,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Les 13 méridiens de passage d'un signe à l'autre, leurs lieux gardiens et l'angle optimal qu'ils donnent</t>
+          <t>Les 13 méridiens de passage d'un signe à l'autre et le lieu qui les garde</t>
         </is>
       </c>
     </row>
@@ -682,7 +686,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Méridien recalculé depuis la phase φ ; villes et écarts établis pour φ = 206,178.</t>
+          <t>Méridien recalculé depuis la phase φ ; villes et écarts établis pour φ = 198,716.</t>
         </is>
       </c>
     </row>
@@ -714,7 +718,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Ville ou lieu (φ = 206,178)</t>
+          <t>Ville ou lieu (φ = 198,716)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -749,17 +753,17 @@
         <f>MOD(Phase-C5+180,360)-180</f>
         <v/>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Port-Vila (Vanuatu)</t>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Pacifique ; îles Salomon (Honiara) à 1,1°</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
@@ -786,19 +790,19 @@
         <f>MOD(Phase-C6+180,360)-180</f>
         <v/>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Melbourne</t>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Mont Fuji ; Adélaïde</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Pléiades = Subaru au Japon ; écho régional</t>
+          <t>0,00 ; 0,13</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Forte : les Pléiades (Subaru) sur la montagne sacrée du Japon</t>
         </is>
       </c>
     </row>
@@ -823,19 +827,19 @@
         <f>MOD(Phase-C7+180,360)-180</f>
         <v/>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Sanctuaire d'Ise ; Kyoto ; Nagoya</t>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Busan ; Gyeongju</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0,34 ; 0,63 ; 0,52</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Forte : étoile royale sur le sanctuaire le plus sacré du shintô</t>
+          <t>0,10 ; 0,28</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Moyenne : l'œil du Taureau sur l'ancienne capitale de Silla</t>
         </is>
       </c>
     </row>
@@ -860,19 +864,19 @@
         <f>MOD(Phase-C8+180,360)-180</f>
         <v/>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Shenyang</t>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Pékin (Cité interdite) ; Perth</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Faible</t>
+          <t>0,25 ; 0,28</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Moyenne : la corne du Taureau sur la capitale impériale</t>
         </is>
       </c>
     </row>
@@ -897,19 +901,19 @@
         <f>MOD(Phase-C9+180,360)-180</f>
         <v/>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Yangon (Shwedagon) ; Mandalay</t>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Kolkata ; Siliguri</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0,2 ; 0,15</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Moyenne : capitales birmanes</t>
+          <t>0,12 ; 0,05</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Coïncidence de métropole</t>
         </is>
       </c>
     </row>
@@ -934,19 +938,19 @@
         <f>MOD(Phase-C10+180,360)-180</f>
         <v/>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Krasnoïarsk</t>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Katmandou ; Patna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Aucune</t>
+          <t>0,18 ; 0,36</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Moyenne : la capitale de l'Himalaya</t>
         </is>
       </c>
     </row>
@@ -971,19 +975,19 @@
         <f>MOD(Phase-C11+180,360)-180</f>
         <v/>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Bhopal ; Delhi</t>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Jamnagar ; Somnath</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0,05 ; 0,22</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Coïncidence de métropole</t>
+          <t>0,07 ; 0,40</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Forte : sous le signe de la Lune, le temple du Seigneur de la Lune</t>
         </is>
       </c>
     </row>
@@ -1008,19 +1012,19 @@
         <f>MOD(Phase-C12+180,360)-180</f>
         <v/>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ahmedabad ; Mumbai</t>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Kandahar ; Boukhara</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0,05 ; 0,35</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Coïncidence de métropole</t>
+          <t>0,63 ; 0,66</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Faible</t>
         </is>
       </c>
     </row>
@@ -1045,19 +1049,19 @@
         <f>MOD(Phase-C13+180,360)-180</f>
         <v/>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Détroit d'Ormuz (Bandar Abbas)</t>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Ahvaz ; Suse</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Forte : étoile royale sur la porte de la Perse (Lion et Soleil)</t>
+          <t>0,20 ; 0,64</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Forte : étoile royale sur Suse, capitale royale de la Perse</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1086,17 @@
         <f>MOD(Phase-C14+180,360)-180</f>
         <v/>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Détroit d'Ormuz (Bandar Abbas)</t>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Kazan ; Ahvaz</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+          <t>0,03 ; 0,41</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Avec Regulus</t>
         </is>
@@ -1119,19 +1123,19 @@
         <f>MOD(Phase-C15+180,360)-180</f>
         <v/>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Jérusalem ; Mersin</t>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Izmir ; Pergame ; Éphèse</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0,66 ; 0,08</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Moyenne : lion de Juda, à la limite</t>
+          <t>0,04 ; 0,08 ; 0,24</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Moyenne : la queue du Lion sur l'Ionie antique</t>
         </is>
       </c>
     </row>
@@ -1156,19 +1160,19 @@
         <f>MOD(Phase-C16+180,360)-180</f>
         <v/>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Vienne</t>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Francfort ; Gênes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Forte : la vendangeuse sur la capitale aux vignes</t>
+          <t>0,10 ; 0,15</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Faible</t>
         </is>
       </c>
     </row>
@@ -1193,19 +1197,19 @@
         <f>MOD(Phase-C17+180,360)-180</f>
         <v/>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Paris</t>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Ouessant ; Fès</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Signature : l'épi sur Paris à 0,01°</t>
+          <t>0,04 ; 0,12</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Signature : l'épi sur la dernière terre de Gaule avant l'océan</t>
         </is>
       </c>
     </row>
@@ -1230,17 +1234,17 @@
         <f>MOD(Phase-C18+180,360)-180</f>
         <v/>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Atlantique ; Islande, Cap-Vert à 1-2°</t>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Atlantique ; Açores (São Miguel)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
@@ -1267,19 +1271,19 @@
         <f>MOD(Phase-C19+180,360)-180</f>
         <v/>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Atlantique ; Praia (Cap-Vert)</t>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Atlantique ; Açores (Flores)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Aucune</t>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Faible : l'île la plus occidentale de l'Europe</t>
         </is>
       </c>
     </row>
@@ -1304,19 +1308,19 @@
         <f>MOD(Phase-C20+180,360)-180</f>
         <v/>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Rio de Janeiro</t>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Macapá (Marco Zero) ; Porto Alegre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0,40</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Moyenne : étoile royale sur la métropole du Brésil</t>
+          <t>0,02 ; 0,19</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Forte : étoile royale sur la ligne de l'équateur, à l'embouchure de l'Amazone</t>
         </is>
       </c>
     </row>
@@ -1341,19 +1345,19 @@
         <f>MOD(Phase-C21+180,360)-180</f>
         <v/>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Buenos Aires</t>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>San Juan (Porto Rico) ; Cochabamba</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Coïncidence de métropole</t>
+          <t>0,23 ; 0,29</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Aucune</t>
         </is>
       </c>
     </row>
@@ -1378,19 +1382,19 @@
         <f>MOD(Phase-C22+180,360)-180</f>
         <v/>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Nuuk (Groenland)</t>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Corrientes ; Manaus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Aucune</t>
+          <t>0,42 ; 0,77</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Faible</t>
         </is>
       </c>
     </row>
@@ -1415,17 +1419,17 @@
         <f>MOD(Phase-C23+180,360)-180</f>
         <v/>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Montevideo</t>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Halifax ; Porto Velho</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+          <t>0,16 ; 0,17</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
@@ -1452,19 +1456,19 @@
         <f>MOD(Phase-C24+180,360)-180</f>
         <v/>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>La Paz</t>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Cali ; Baltimore ; Washington</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Aucune</t>
+          <t>0,16 ; 0,25 ; 0,68</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Faible</t>
         </is>
       </c>
     </row>
@@ -1489,17 +1493,17 @@
         <f>MOD(Phase-C25+180,360)-180</f>
         <v/>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Cali ; Lima</t>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>San José (Costa Rica) ; Atlanta</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0,31 ; 0,82</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+          <t>0,41 ; 0,72</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
@@ -1526,19 +1530,19 @@
         <f>MOD(Phase-C26+180,360)-180</f>
         <v/>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Austin ; Teotihuacan</t>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Taos Pueblo ; Denver</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0,13 ; 0,97</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Faible</t>
+          <t>0,22 ; 0,35</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Moyenne : l'un des plus anciens villages habités d'Amérique du Nord</t>
         </is>
       </c>
     </row>
@@ -1563,19 +1567,19 @@
         <f>MOD(Phase-C27+180,360)-180</f>
         <v/>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>San Diego ; Tijuana</t>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Pacifique, côte des séquoias (cap Mendocino)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0,20 ; 0,36</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Moyenne : frontière de deux signes et deux pays</t>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Aucune</t>
         </is>
       </c>
     </row>
@@ -1600,17 +1604,17 @@
         <f>MOD(Phase-C28+180,360)-180</f>
         <v/>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>San Diego ; Tijuana</t>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Pacifique, côte des séquoias (cap Mendocino)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0,05 ; 0,21</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Avec Deneb Algedi</t>
         </is>
@@ -1637,19 +1641,19 @@
         <f>MOD(Phase-C29+180,360)-180</f>
         <v/>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Pacifique, au large du Canada</t>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Juneau (Alaska)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Le porteur d'eau sur l'océan</t>
+          <t>0,21</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Moyenne : le porteur d'eau sur la côte des peuples du saumon</t>
         </is>
       </c>
     </row>
@@ -1674,19 +1678,19 @@
         <f>MOD(Phase-C30+180,360)-180</f>
         <v/>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Fidji (Suva)</t>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Christchurch</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0,9</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Antiméridien, ligne de changement de date</t>
+          <t>0,74</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Aucune</t>
         </is>
       </c>
     </row>
@@ -1711,19 +1715,19 @@
         <f>MOD(Phase-C31+180,360)-180</f>
         <v/>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Fidji (Suva)</t>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Aoraki / mont Cook</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Le nœud des Poissons près de l'antiméridien</t>
+          <t>0,80</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Moyenne : la montagne ancêtre des Ngāi Tahu</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1810,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Ville ≥ 500 000 hab. la plus proche (φ = 206,178)</t>
+          <t>Ville ≥ 500 000 hab. la plus proche (φ = 198,716)</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -1859,7 +1863,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1.77</v>
+        <v>9.23</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1867,7 +1871,7 @@
         </is>
       </c>
       <c r="K5" s="4" t="n">
-        <v>36.26</v>
+        <v>28.81</v>
       </c>
     </row>
     <row r="6">
@@ -1904,7 +1908,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.56</v>
+        <v>10.02</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1912,7 +1916,7 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>35.48</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="7">
@@ -1949,7 +1953,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>19.29</v>
+        <v>26.75</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1957,7 +1961,7 @@
         </is>
       </c>
       <c r="K7" s="4" t="n">
-        <v>43.28</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="8">
@@ -1990,19 +1994,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hanzhong</t>
+          <t>Baoshan</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.05</v>
+        <v>0.45</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Xi'an</t>
+          <t>Angkor</t>
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.87</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="9">
@@ -2035,19 +2039,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tiruchirappalli</t>
+          <t>Jalalpur Pirwala</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Samarcande</t>
         </is>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.43</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="10">
@@ -2080,19 +2084,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tbilisi</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Babylone</t>
+          <t>Moscou</t>
         </is>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="11">
@@ -2125,19 +2129,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Üsküdar</t>
+          <t>Pristina</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Delphes</t>
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.03</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2170,7 +2174,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Zagreb</t>
+          <t>Kano</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
@@ -2178,11 +2182,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Carthage</t>
         </is>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.33</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="13">
@@ -2215,19 +2219,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Prague</t>
+          <t>Aba</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Aix-la-Chapelle</t>
         </is>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="14">
@@ -2260,11 +2264,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>João Pessoa</t>
+          <t>Aracaju</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.9</v>
+        <v>0.65</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -2272,7 +2276,7 @@
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>20.42</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="15">
@@ -2305,19 +2309,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Maceió</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.66</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Saint-Jacques</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="K15" s="4" t="n">
-        <v>27.85</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="16">
@@ -2350,11 +2354,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.78</v>
+        <v>0.26</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2362,7 +2366,7 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>12.81</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="17">
@@ -2395,11 +2399,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2407,7 +2411,7 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>12.55</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="18">
@@ -2440,19 +2444,19 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Santo Domingo Oeste</t>
+          <t>Callao</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.14</v>
+        <v>0.47</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Cusco</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.83</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -2485,19 +2489,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Callao</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Chichén Itzá</t>
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.42</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="20">
@@ -2530,11 +2534,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Mexicali</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2542,7 +2546,7 @@
         </is>
       </c>
       <c r="K20" s="4" t="n">
-        <v>16.48</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="21">
@@ -2579,7 +2583,7 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>7.42</v>
+        <v>14.87</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2587,7 +2591,7 @@
         </is>
       </c>
       <c r="K21" s="4" t="n">
-        <v>31.41</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="22">
@@ -2624,7 +2628,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9.58</v>
+        <v>17.03</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2632,7 +2636,7 @@
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>33.57</v>
+        <v>41.02</v>
       </c>
     </row>
   </sheetData>
@@ -3046,66 +3050,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>L'équilibre par moindres carrés</t>
+          <t>Le calage par moindres carrés</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Étoiles et lieux restent rigides ; seule la rotation φ varie. Écart = méridien de l'étoile (φ − λ) − longitude du lieu. L'angle optimal rend minimale la somme des carrés des écarts : φ* = φ − moyenne des écarts.</t>
+          <t>Chaque étoile face au lieu de référence le plus proche ; φ* est la phase qui rend minimale la somme des carrés. Le lieu le plus proche change avec φ : les colonnes C-D valent pour φ = 198,716.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Couple (étoile ou point du ciel)</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Étoile</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>λ écliptique (°)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Lieu</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Lieu de référence le plus proche</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Longitude du lieu (°, Est +)</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Méridien de l'étoile (°)</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Écart (°)</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Inclus (&lt; 1° à 206,178)</t>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Carré de l'écart</t>
         </is>
       </c>
     </row>
@@ -3116,15 +3120,15 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>37.66</v>
+        <v>37.662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Port-Vila</t>
+          <t>Ise</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>168.318</v>
+        <v>136.73</v>
       </c>
       <c r="E5" s="4">
         <f>MOD(Phase-B5+180,360)-180</f>
@@ -3134,10 +3138,9 @@
         <f>MOD(E5-D5+180,360)-180</f>
         <v/>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G5" s="4">
+        <f>F5^2</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -3147,15 +3150,15 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>59.99</v>
+        <v>59.992</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Melbourne</t>
+          <t>Ise</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>144.988</v>
+        <v>136.73</v>
       </c>
       <c r="E6" s="4">
         <f>MOD(Phase-B6+180,360)-180</f>
@@ -3165,10 +3168,9 @@
         <f>MOD(E6-D6+180,360)-180</f>
         <v/>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
+      <c r="G6" s="4">
+        <f>F6^2</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -3178,15 +3180,15 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>69.79000000000001</v>
+        <v>69.789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ise</t>
+          <t>Kyoto</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>136.728</v>
+        <v>135.77</v>
       </c>
       <c r="E7" s="4">
         <f>MOD(Phase-B7+180,360)-180</f>
@@ -3196,10 +3198,9 @@
         <f>MOD(E7-D7+180,360)-180</f>
         <v/>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G7" s="4">
+        <f>F7^2</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -3209,15 +3210,15 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>82.56999999999999</v>
+        <v>82.575</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shenyang</t>
+          <t>Pékin</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>123.438</v>
+        <v>116.4</v>
       </c>
       <c r="E8" s="4">
         <f>MOD(Phase-B8+180,360)-180</f>
@@ -3227,10 +3228,9 @@
         <f>MOD(E8-D8+180,360)-180</f>
         <v/>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G8" s="4">
+        <f>F8^2</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -3244,11 +3244,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yangon</t>
+          <t>Lhassa</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>96.13800000000001</v>
+        <v>91.17</v>
       </c>
       <c r="E9" s="4">
         <f>MOD(Phase-B9+180,360)-180</f>
@@ -3258,10 +3258,9 @@
         <f>MOD(E9-D9+180,360)-180</f>
         <v/>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G9" s="4">
+        <f>F9^2</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -3271,15 +3270,15 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>113.22</v>
+        <v>113.216</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Krasnoïarsk</t>
+          <t>Bodh-Gaya</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>92.928</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="E10" s="4">
         <f>MOD(Phase-B10+180,360)-180</f>
@@ -3289,10 +3288,9 @@
         <f>MOD(E10-D10+180,360)-180</f>
         <v/>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G10" s="4">
+        <f>F10^2</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3302,15 +3300,15 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>128.72</v>
+        <v>128.722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Samarcande</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>77.408</v>
+        <v>66.97</v>
       </c>
       <c r="E11" s="4">
         <f>MOD(Phase-B11+180,360)-180</f>
@@ -3320,10 +3318,9 @@
         <f>MOD(E11-D11+180,360)-180</f>
         <v/>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G11" s="4">
+        <f>F11^2</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3333,15 +3330,15 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>133.64</v>
+        <v>133.642</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Boukhara</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>72.58799999999999</v>
+        <v>64.42</v>
       </c>
       <c r="E12" s="4">
         <f>MOD(Phase-B12+180,360)-180</f>
@@ -3351,10 +3348,9 @@
         <f>MOD(E12-D12+180,360)-180</f>
         <v/>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G12" s="4">
+        <f>F12^2</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -3364,15 +3360,15 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>149.83</v>
+        <v>149.829</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ormuz (Bandar Abbas)</t>
+          <t>Ispahan</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>56.268</v>
+        <v>51.67</v>
       </c>
       <c r="E13" s="4">
         <f>MOD(Phase-B13+180,360)-180</f>
@@ -3382,10 +3378,9 @@
         <f>MOD(E13-D13+180,360)-180</f>
         <v/>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G13" s="4">
+        <f>F13^2</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -3395,15 +3390,15 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>149.62</v>
+        <v>149.615</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ormuz (Bandar Abbas)</t>
+          <t>Ispahan</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>56.268</v>
+        <v>51.67</v>
       </c>
       <c r="E14" s="4">
         <f>MOD(Phase-B14+180,360)-180</f>
@@ -3413,10 +3408,9 @@
         <f>MOD(E14-D14+180,360)-180</f>
         <v/>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G14" s="4">
+        <f>F14^2</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3426,15 +3420,15 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>171.62</v>
+        <v>171.618</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jérusalem</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>35.218</v>
+        <v>28.98</v>
       </c>
       <c r="E15" s="4">
         <f>MOD(Phase-B15+180,360)-180</f>
@@ -3444,10 +3438,9 @@
         <f>MOD(E15-D15+180,360)-180</f>
         <v/>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G15" s="4">
+        <f>F15^2</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -3461,11 +3454,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Carthage</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>16.368</v>
+        <v>10.32</v>
       </c>
       <c r="E16" s="4">
         <f>MOD(Phase-B16+180,360)-180</f>
@@ -3475,10 +3468,9 @@
         <f>MOD(E16-D16+180,360)-180</f>
         <v/>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G16" s="4">
+        <f>F16^2</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -3488,15 +3480,15 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>203.84</v>
+        <v>203.841</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cordoue</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.348</v>
+        <v>-4.78</v>
       </c>
       <c r="E17" s="4">
         <f>MOD(Phase-B17+180,360)-180</f>
@@ -3506,28 +3498,27 @@
         <f>MOD(E17-D17+180,360)-180</f>
         <v/>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G17" s="4">
+        <f>F17^2</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Zubeneschamali</t>
+          <t>Zubenelgenubi</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>229.37</v>
+        <v>225.083</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Praia</t>
+          <t>Saint-Jacques</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-23.512</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="E18" s="4">
         <f>MOD(Phase-B18+180,360)-180</f>
@@ -3537,28 +3528,27 @@
         <f>MOD(E18-D18+180,360)-180</f>
         <v/>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G18" s="4">
+        <f>F18^2</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Antares</t>
+          <t>Zubeneschamali</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>249.76</v>
+        <v>229.372</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Saint-Jacques</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-43.182</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="E19" s="4">
         <f>MOD(Phase-B19+180,360)-180</f>
@@ -3568,28 +3558,27 @@
         <f>MOD(E19-D19+180,360)-180</f>
         <v/>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G19" s="4">
+        <f>F19^2</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shaula</t>
+          <t>Antares</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>264.59</v>
+        <v>249.762</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-58.382</v>
+        <v>-71.97</v>
       </c>
       <c r="E20" s="4">
         <f>MOD(Phase-B20+180,360)-180</f>
@@ -3599,28 +3588,27 @@
         <f>MOD(E20-D20+180,360)-180</f>
         <v/>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G20" s="4">
+        <f>F20^2</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sabik</t>
+          <t>Shaula</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>257.97</v>
+        <v>264.586</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nuuk</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-51.742</v>
+        <v>-71.97</v>
       </c>
       <c r="E21" s="4">
         <f>MOD(Phase-B21+180,360)-180</f>
@@ -3630,28 +3618,27 @@
         <f>MOD(E21-D21+180,360)-180</f>
         <v/>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G21" s="4">
+        <f>F21^2</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rasalhague</t>
+          <t>Sabik</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>262.45</v>
+        <v>257.97</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Montevideo</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-56.192</v>
+        <v>-71.97</v>
       </c>
       <c r="E22" s="4">
         <f>MOD(Phase-B22+180,360)-180</f>
@@ -3661,28 +3648,27 @@
         <f>MOD(E22-D22+180,360)-180</f>
         <v/>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G22" s="4">
+        <f>F22^2</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kaus Australis</t>
+          <t>Rasalhague</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>275.08</v>
+        <v>262.449</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-68.152</v>
+        <v>-71.97</v>
       </c>
       <c r="E23" s="4">
         <f>MOD(Phase-B23+180,360)-180</f>
@@ -3692,28 +3678,27 @@
         <f>MOD(E23-D23+180,360)-180</f>
         <v/>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G23" s="4">
+        <f>F23^2</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nunki</t>
+          <t>Kaus Australis</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>282.39</v>
+        <v>275.079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-76.52200000000001</v>
+        <v>-77.04000000000001</v>
       </c>
       <c r="E24" s="4">
         <f>MOD(Phase-B24+180,360)-180</f>
@@ -3723,28 +3708,27 @@
         <f>MOD(E24-D24+180,360)-180</f>
         <v/>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G24" s="4">
+        <f>F24^2</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dabih</t>
+          <t>Nunki</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>304.05</v>
+        <v>282.385</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Chichén Itzá</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-97.742</v>
+        <v>-88.56999999999999</v>
       </c>
       <c r="E25" s="4">
         <f>MOD(Phase-B25+180,360)-180</f>
@@ -3754,28 +3738,27 @@
         <f>MOD(E25-D25+180,360)-180</f>
         <v/>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G25" s="4">
+        <f>F25^2</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deneb Algedi</t>
+          <t>Dabih</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>323.54</v>
+        <v>304.047</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-117.162</v>
+        <v>-99.13</v>
       </c>
       <c r="E26" s="4">
         <f>MOD(Phase-B26+180,360)-180</f>
@@ -3785,28 +3768,27 @@
         <f>MOD(E26-D26+180,360)-180</f>
         <v/>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G26" s="4">
+        <f>F26^2</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sadalsuud</t>
+          <t>Deneb Algedi</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>323.4</v>
+        <v>323.543</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-117.172</v>
+        <v>-99.13</v>
       </c>
       <c r="E27" s="4">
         <f>MOD(Phase-B27+180,360)-180</f>
@@ -3816,28 +3798,27 @@
         <f>MOD(E27-D27+180,360)-180</f>
         <v/>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G27" s="4">
+        <f>F27^2</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alpherg (η Psc)</t>
+          <t>Sadalsuud</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>26.82</v>
+        <v>323.395</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suva (Fidji)</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>178.458</v>
+        <v>-99.13</v>
       </c>
       <c r="E28" s="4">
         <f>MOD(Phase-B28+180,360)-180</f>
@@ -3847,28 +3828,27 @@
         <f>MOD(E28-D28+180,360)-180</f>
         <v/>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
+      <c r="G28" s="4">
+        <f>F28^2</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alrescha</t>
+          <t>Sadalmelik</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>29.38</v>
+        <v>333.352</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Suva (Fidji)</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>178.398</v>
+        <v>-99.13</v>
       </c>
       <c r="E29" s="4">
         <f>MOD(Phase-B29+180,360)-180</f>
@@ -3878,28 +3858,27 @@
         <f>MOD(E29-D29+180,360)-180</f>
         <v/>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
+      <c r="G29" s="4">
+        <f>F29^2</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Porte Vierge – Lion (limite UAI)</t>
+          <t>Alpherg (η Psc)</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>174.15</v>
+        <v>26.816</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sphinx de Gizeh</t>
+          <t>Ise</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>31.138</v>
+        <v>136.73</v>
       </c>
       <c r="E30" s="4">
         <f>MOD(Phase-B30+180,360)-180</f>
@@ -3909,102 +3888,231 @@
         <f>MOD(E30-D30+180,360)-180</f>
         <v/>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Ajustement</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>φ optimal (°)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Écart quadratique moyen (°)</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Δ avec la phase (°)</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>Spica tombe à (°, Est +)</t>
-        </is>
+      <c r="G30" s="4">
+        <f>F30^2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Alrescha</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>29.379</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ise</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>136.73</v>
+      </c>
+      <c r="E31" s="4">
+        <f>MOD(Phase-B31+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="F31" s="4">
+        <f>MOD(E31-D31+180,360)-180</f>
+        <v/>
+      </c>
+      <c r="G31" s="4">
+        <f>F31^2</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Équilibre des 26 couples, Sphinx compris</t>
-        </is>
-      </c>
-      <c r="B33" s="9">
-        <f>Phase-AVERAGE(F5:F30)</f>
-        <v/>
-      </c>
-      <c r="C33" s="4">
-        <f>SQRT(SUMPRODUCT((F5:F30-AVERAGE(F5:F30))^2)/COUNT(F5:F30))</f>
-        <v/>
-      </c>
-      <c r="D33" s="9">
-        <f>ABS(B33-Phase)</f>
-        <v/>
-      </c>
-      <c r="E33" s="4">
-        <f>MOD(B33-203.841+180,360)-180</f>
+          <t>Somme des carrés</t>
+        </is>
+      </c>
+      <c r="B33" s="11">
+        <f>SUM(G5:G31)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Les 25 couples étoile – lieu, sans le Sphinx</t>
+          <t>φ* = phase − écart moyen (affinage)</t>
         </is>
       </c>
       <c r="B34" s="9">
-        <f>Phase-AVERAGE(F5:F29)</f>
-        <v/>
-      </c>
-      <c r="C34" s="4">
-        <f>SQRT(SUMPRODUCT((F5:F29-AVERAGE(F5:F29))^2)/COUNT(F5:F29))</f>
-        <v/>
-      </c>
-      <c r="D34" s="9">
-        <f>ABS(B34-Phase)</f>
-        <v/>
-      </c>
-      <c r="E34" s="4">
-        <f>MOD(B34-203.841+180,360)-180</f>
+        <f>Phase-AVERAGE(F5:F31)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Couples à moins d'un degré, Sphinx compris</t>
-        </is>
-      </c>
-      <c r="B35" s="9">
-        <f>Phase-AVERAGEIF(G5:G30,"oui",F5:F30)</f>
-        <v/>
-      </c>
-      <c r="D35" s="9">
-        <f>ABS(B35-Phase)</f>
-        <v/>
-      </c>
-      <c r="E35" s="4">
-        <f>MOD(B35-203.841+180,360)-180</f>
-        <v/>
+          <t>Étoiles à moins de 1°</t>
+        </is>
+      </c>
+      <c r="B35">
+        <f>COUNTIFS(F5:F31,"&lt;1",F5:F31,"&gt;-1")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Spica tombe à (°, Est +)</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <f>MOD(Phase-203.841+180,360)-180</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Balayage de 7 200 positions (pas 0,05°)</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>φ (°)</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Spica tombe à (°, Est +)</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Étoiles à moins de 1°</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Somme des carrés</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Calage retenu : Spica sur Ouessant</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>198.716</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-5.125</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7128.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Deuxième vallée</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-154.291</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11416.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Troisième vallée</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C41" t="n">
+        <v>173.959</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>11548</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Quatrième vallée</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-166.691</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" t="n">
+        <v>11602.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cinquième vallée</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>176.759</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>11618.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ancien calage : Spica sur Paris</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>206.178</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2.337</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8049.6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Toutes les positions dont la somme reste sous 11 000 se tiennent entre 175° et 216° : une seule vallée, dont le fond est 198,716°. L'ancien calage 206,178° est au 328e rang sur 7 200.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4018,17 +4126,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4041,47 +4149,47 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Les 13 méridiens où un signe passe au suivant, et le lieu remarquable le plus proche. « Gardée » : un monument ou un lieu sacré à moins d'un degré. L'angle optimal se recalcule à partir de la phase.</t>
+          <t>Les 13 méridiens où un signe passe au suivant, et le lieu qui se tient sur chacun. Lues après le calage, hors du calcul.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Porte</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>λ de la frontière (°)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Lieu</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Longitude du lieu (°, Est +)</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Méridien de la porte (°)</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Écart (°)</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Gardée</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Nature du lieu</t>
         </is>
@@ -4090,19 +4198,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bélier | Taureau</t>
+          <t>Poissons | Bélier</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>53.47</v>
+        <v>29.09</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brisbane</t>
+          <t>Mont Yasur, Tanna</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>153.03</v>
+        <v>169.447</v>
       </c>
       <c r="E5" s="4">
         <f>MOD(Phase-B5+180,360)-180</f>
@@ -4114,31 +4222,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ville moderne</t>
+          <t>Volcan qu'on appelle le phare du Pacifique, montagne sacrée de Tanna</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Taureau | Gémeaux</t>
+          <t>Bélier | Taureau</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>90.43000000000001</v>
+        <v>53.47</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Grande Muraille, Badaling</t>
+          <t>Melbourne</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>116.016</v>
+        <v>144.963</v>
       </c>
       <c r="E6" s="4">
         <f>MOD(Phase-B6+180,360)-180</f>
@@ -4150,31 +4258,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Frontière bâtie de la Chine ; Cité interdite à 0,65°</t>
+          <t>Ville moderne</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gémeaux | Cancer</t>
+          <t>Taureau | Gémeaux</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>118.26</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kangchenjunga</t>
+          <t>Xi'an (Chang'an)</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>88.14700000000001</v>
+        <v>108.94</v>
       </c>
       <c r="E7" s="4">
         <f>MOD(Phase-B7+180,360)-180</f>
@@ -4191,26 +4299,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Troisième sommet du monde, montagne sacrée du Sikkim</t>
+          <t>Capitale des Zhou, des Han et des Tang, départ de la route de la soie</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cancer | Lion</t>
+          <t>Gémeaux | Cancer</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>138.18</v>
+        <v>118.26</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Anuradhapura</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>68.13800000000001</v>
+        <v>80.396</v>
       </c>
       <c r="E8" s="4">
         <f>MOD(Phase-B8+180,360)-180</f>
@@ -4227,26 +4335,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Cité de l'Indus, le Grand Bain</t>
+          <t>Le figuier sacré Sri Maha Bodhi, bouture de l'arbre de l'Éveil</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lion | Vierge</t>
+          <t>Cancer | Lion</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>174.15</v>
+        <v>138.18</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sphinx de Gizeh</t>
+          <t>Iekaterinbourg</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>31.138</v>
+        <v>60.606</v>
       </c>
       <c r="E9" s="4">
         <f>MOD(Phase-B9+180,360)-180</f>
@@ -4263,26 +4371,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Le gardien à corps de lion ; Léontopolis à 0,69°</t>
+          <t>Ville de l'Oural, sur la frontière de l'Europe et de l'Asie</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vierge | Balance</t>
+          <t>Lion | Vierge</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>218.13</v>
+        <v>174.15</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ouadane</t>
+          <t>Mont Athos</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-11.62</v>
+        <v>24.326</v>
       </c>
       <c r="E10" s="4">
         <f>MOD(Phase-B10+180,360)-180</f>
@@ -4299,26 +4407,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Ksar caravanier, UNESCO ; Chinguetti à 0,41°</t>
+          <t>La Sainte Montagne, jardin de la Vierge</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Balance | Scorpion</t>
+          <t>Vierge | Balance</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>241.05</v>
+        <v>218.13</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Olinda</t>
+          <t>Hekla</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-34.855</v>
+        <v>-19.7</v>
       </c>
       <c r="E11" s="4">
         <f>MOD(Phase-B11+180,360)-180</f>
@@ -4335,18 +4443,18 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Ville historique, UNESCO ; Ponta do Seixas, point le plus oriental des Amériques, à 0,08°</t>
+          <t>Le volcan que le Moyen Âge appelait la porte de l'enfer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scorpion | Ophiuchus</t>
+          <t>Balance | Scorpion</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>247.68</v>
+        <v>241.05</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4378,19 +4486,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ophiuchus | Sagittaire</t>
+          <t>Scorpion | Ophiuchus</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>266.25</v>
+        <v>247.68</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rencontre des eaux, Manaus</t>
+          <t>Belém</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-59.9</v>
+        <v>-48.49</v>
       </c>
       <c r="E13" s="4">
         <f>MOD(Phase-B13+180,360)-180</f>
@@ -4407,26 +4515,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Rio Negro et Solimões côte à côte sans se mêler</t>
+          <t>Porte de l'Amazone ; le Círio de Nazaré, grande procession mariale</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sagittaire | Capricorne</t>
+          <t>Ophiuchus | Sagittaire</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>299.71</v>
+        <v>266.25</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>La Venta</t>
+          <t>Salar d'Uyuni</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-94.04000000000001</v>
+        <v>-67.489</v>
       </c>
       <c r="E14" s="4">
         <f>MOD(Phase-B14+180,360)-180</f>
@@ -4443,26 +4551,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Grande cité olmèque, pyramide et têtes colossales</t>
+          <t>Le plus grand miroir de la Terre, où le ciel se pose sur le sol</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Capricorne | Verseau</t>
+          <t>Sagittaire | Capricorne</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>327.88</v>
+        <v>299.71</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mont Hood (Wy'east)</t>
+          <t>Wirikuta (Real de Catorce)</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-121.696</v>
+        <v>-100.885</v>
       </c>
       <c r="E15" s="4">
         <f>MOD(Phase-B15+180,360)-180</f>
@@ -4479,34 +4587,33 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Montagne de la légende du Pont des Dieux</t>
+          <t>Désert sacré des Huichols, où le soleil est né</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Verseau | Poissons</t>
+          <t>Capricorne | Verseau</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>351.57</v>
+        <v>327.88</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Valdez</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>-146.35</v>
-      </c>
+          <t>Côte de Colombie-Britannique</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n"/>
       <c r="E16" s="4">
         <f>MOD(Phase-B16+180,360)-180</f>
         <v/>
       </c>
-      <c r="F16" s="4">
-        <f>MOD(E16-D16+180,360)-180</f>
-        <v/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -4515,26 +4622,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Port d'Alaska</t>
+          <t>Aucun lieu marquant</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Poissons | Bélier</t>
+          <t>Verseau | Poissons</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>29.09</v>
+        <v>351.57</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Whakaari</t>
+          <t>Kodiak</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>177.18</v>
+        <v>-152.407</v>
       </c>
       <c r="E17" s="4">
         <f>MOD(Phase-B17+180,360)-180</f>
@@ -4546,104 +4653,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Volcan actif de Nouvelle-Zélande</t>
+          <t>Île d'Alaska</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Ajustement</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>φ optimal (°)</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Écart quadratique moyen (°)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Δ avec la phase (°)</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Spica tombe à (°, Est +)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Les 10 portes gardées</t>
-        </is>
-      </c>
-      <c r="B20" s="9">
-        <f>Phase-AVERAGEIF(G5:G17,"oui",F5:F17)</f>
-        <v/>
-      </c>
-      <c r="C20" s="4">
-        <f>SQRT(SUMPRODUCT((G5:G17="oui")*(F5:F17-AVERAGEIF(G5:G17,"oui",F5:F17))^2)/COUNTIF(G5:G17,"oui"))</f>
-        <v/>
-      </c>
-      <c r="D20" s="9">
-        <f>ABS(B20-Phase)</f>
-        <v/>
-      </c>
-      <c r="E20" s="4">
-        <f>MOD(B20-203.841+180,360)-180</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Les 13 portes</t>
-        </is>
-      </c>
-      <c r="B21" s="9">
-        <f>Phase-AVERAGE(F5:F17)</f>
-        <v/>
-      </c>
-      <c r="C21" s="4">
-        <f>SQRT(SUMPRODUCT((F5:F17-AVERAGE(F5:F17))^2)/COUNT(F5:F17))</f>
-        <v/>
-      </c>
-      <c r="D21" s="9">
-        <f>ABS(B21-Phase)</f>
-        <v/>
-      </c>
-      <c r="E21" s="4">
-        <f>MOD(B21-203.841+180,360)-180</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>25 couples étoile – lieu + 10 portes gardées</t>
-        </is>
-      </c>
-      <c r="B22" s="9">
-        <f>Phase-(SUM('Moindres carrés'!F5:F29)+SUMIF(G5:G17,"oui",F5:F17))/(25+COUNTIF(G5:G17,"oui"))</f>
-        <v/>
-      </c>
-      <c r="D22" s="9">
-        <f>ABS(B22-Phase)</f>
-        <v/>
-      </c>
-      <c r="E22" s="4">
-        <f>MOD(B22-203.841+180,360)-180</f>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Portes gardées</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>COUNTIF(G5:G17,"oui")</f>
         <v/>
       </c>
     </row>
